--- a/Planilhas/Consolidada3Planilhas.xlsx
+++ b/Planilhas/Consolidada3Planilhas.xlsx
@@ -424,17 +424,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Valor (08/09/2026)</t>
+          <t>Valor (10/09/2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Valor (07/09/2026)</t>
+          <t>Valor (09/09/2026)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Valor (06/09/2026)</t>
+          <t>Valor (08/09/2026)</t>
         </is>
       </c>
     </row>
@@ -443,13 +443,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>13.601</v>
+        <v>13.651</v>
       </c>
       <c r="C2" t="n">
-        <v>13.601</v>
+        <v>13.651</v>
       </c>
       <c r="D2" t="n">
-        <v>13.601</v>
+        <v>13.651</v>
       </c>
     </row>
     <row r="3">
@@ -457,13 +457,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>20.356</v>
+        <v>20.516</v>
       </c>
       <c r="C3" t="n">
-        <v>20.356</v>
+        <v>20.516</v>
       </c>
       <c r="D3" t="n">
-        <v>20.356</v>
+        <v>20.516</v>
       </c>
     </row>
     <row r="4">
@@ -471,13 +471,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>13.816</v>
+        <v>13.879</v>
       </c>
       <c r="C4" t="n">
-        <v>13.816</v>
+        <v>13.879</v>
       </c>
       <c r="D4" t="n">
-        <v>13.816</v>
+        <v>13.879</v>
       </c>
     </row>
     <row r="5">
@@ -485,13 +485,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>20.625</v>
+        <v>20.859</v>
       </c>
       <c r="C5" t="n">
-        <v>20.625</v>
+        <v>20.859</v>
       </c>
       <c r="D5" t="n">
-        <v>20.625</v>
+        <v>20.859</v>
       </c>
     </row>
     <row r="6">
@@ -499,13 +499,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>16.848</v>
+        <v>16.989</v>
       </c>
       <c r="C6" t="n">
-        <v>16.848</v>
+        <v>16.989</v>
       </c>
       <c r="D6" t="n">
-        <v>16.848</v>
+        <v>16.989</v>
       </c>
     </row>
     <row r="7">
@@ -513,13 +513,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>31.789</v>
+        <v>32.002</v>
       </c>
       <c r="C7" t="n">
-        <v>31.789</v>
+        <v>32.002</v>
       </c>
       <c r="D7" t="n">
-        <v>31.789</v>
+        <v>32.002</v>
       </c>
     </row>
     <row r="8">
@@ -527,13 +527,13 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>16.728</v>
+        <v>16.808</v>
       </c>
       <c r="C8" t="n">
-        <v>16.728</v>
+        <v>16.808</v>
       </c>
       <c r="D8" t="n">
-        <v>16.728</v>
+        <v>16.808</v>
       </c>
     </row>
     <row r="9">
@@ -541,13 +541,13 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>26.114</v>
+        <v>26.434</v>
       </c>
       <c r="C9" t="n">
-        <v>26.114</v>
+        <v>26.434</v>
       </c>
       <c r="D9" t="n">
-        <v>26.114</v>
+        <v>26.434</v>
       </c>
     </row>
     <row r="10">
@@ -555,13 +555,13 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>1.24</v>
+        <v>1.241</v>
       </c>
       <c r="C10" t="n">
-        <v>1.24</v>
+        <v>1.241</v>
       </c>
       <c r="D10" t="n">
-        <v>1.24</v>
+        <v>1.241</v>
       </c>
     </row>
     <row r="11">
@@ -569,13 +569,13 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-999998.172</v>
+        <v>-999998.153</v>
       </c>
       <c r="C11" t="n">
-        <v>-999998.172</v>
+        <v>-999998.153</v>
       </c>
       <c r="D11" t="n">
-        <v>-999998.172</v>
+        <v>-999998.153</v>
       </c>
     </row>
   </sheetData>

--- a/Planilhas/Consolidada3Planilhas.xlsx
+++ b/Planilhas/Consolidada3Planilhas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,17 +424,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Valor (10/09/2026)</t>
+          <t>Valor (07/10/2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Valor (09/09/2026)</t>
+          <t>Valor (06/10/2026)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Valor (08/09/2026)</t>
+          <t>Valor (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -443,13 +443,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>13.651</v>
+        <v>15.478</v>
       </c>
       <c r="C2" t="n">
-        <v>13.651</v>
+        <v>15.478</v>
       </c>
       <c r="D2" t="n">
-        <v>13.651</v>
+        <v>15.478</v>
       </c>
     </row>
     <row r="3">
@@ -457,13 +457,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>20.516</v>
+        <v>9.705</v>
       </c>
       <c r="C3" t="n">
-        <v>20.516</v>
+        <v>9.705</v>
       </c>
       <c r="D3" t="n">
-        <v>20.516</v>
+        <v>9.705</v>
       </c>
     </row>
     <row r="4">
@@ -471,13 +471,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>13.879</v>
+        <v>31.238</v>
       </c>
       <c r="C4" t="n">
-        <v>13.879</v>
+        <v>31.238</v>
       </c>
       <c r="D4" t="n">
-        <v>13.879</v>
+        <v>31.238</v>
       </c>
     </row>
     <row r="5">
@@ -485,13 +485,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>20.859</v>
+        <v>41.017</v>
       </c>
       <c r="C5" t="n">
-        <v>20.859</v>
+        <v>41.017</v>
       </c>
       <c r="D5" t="n">
-        <v>20.859</v>
+        <v>41.017</v>
       </c>
     </row>
     <row r="6">
@@ -499,13 +499,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>16.989</v>
+        <v>14.185</v>
       </c>
       <c r="C6" t="n">
-        <v>16.989</v>
+        <v>14.185</v>
       </c>
       <c r="D6" t="n">
-        <v>16.989</v>
+        <v>14.185</v>
       </c>
     </row>
     <row r="7">
@@ -513,13 +513,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>32.002</v>
+        <v>10.583</v>
       </c>
       <c r="C7" t="n">
-        <v>32.002</v>
+        <v>10.583</v>
       </c>
       <c r="D7" t="n">
-        <v>32.002</v>
+        <v>10.583</v>
       </c>
     </row>
     <row r="8">
@@ -527,13 +527,13 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>16.808</v>
+        <v>18.226</v>
       </c>
       <c r="C8" t="n">
-        <v>16.808</v>
+        <v>18.226</v>
       </c>
       <c r="D8" t="n">
-        <v>16.808</v>
+        <v>18.226</v>
       </c>
     </row>
     <row r="9">
@@ -541,13 +541,13 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>26.434</v>
+        <v>-592.8819999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>26.434</v>
+        <v>-592.8819999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>26.434</v>
+        <v>-592.8819999999999</v>
       </c>
     </row>
     <row r="10">
@@ -555,13 +555,13 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>1.241</v>
+        <v>11.776</v>
       </c>
       <c r="C10" t="n">
-        <v>1.241</v>
+        <v>11.776</v>
       </c>
       <c r="D10" t="n">
-        <v>1.241</v>
+        <v>11.776</v>
       </c>
     </row>
     <row r="11">
@@ -569,13 +569,237 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-999998.153</v>
+        <v>15.94</v>
       </c>
       <c r="C11" t="n">
-        <v>-999998.153</v>
+        <v>15.94</v>
       </c>
       <c r="D11" t="n">
-        <v>-999998.153</v>
+        <v>15.94</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-1.908</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.908</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.908</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B14" t="n">
+        <v>16.035</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16.035</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.035</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8.266999999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8.266999999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8.266999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4000003.163</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4000003.163</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4000003.163</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.971</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B18" t="n">
+        <v>697.029</v>
+      </c>
+      <c r="C18" t="n">
+        <v>697.029</v>
+      </c>
+      <c r="D18" t="n">
+        <v>697.029</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23</v>
+      </c>
+      <c r="B19" t="n">
+        <v>300.796</v>
+      </c>
+      <c r="C19" t="n">
+        <v>300.796</v>
+      </c>
+      <c r="D19" t="n">
+        <v>300.796</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>24</v>
+      </c>
+      <c r="B20" t="n">
+        <v>156.131</v>
+      </c>
+      <c r="C20" t="n">
+        <v>156.131</v>
+      </c>
+      <c r="D20" t="n">
+        <v>156.131</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>25</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8.884</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8.884</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8.884</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B22" t="n">
+        <v>16.743</v>
+      </c>
+      <c r="C22" t="n">
+        <v>16.743</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16.743</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>27</v>
+      </c>
+      <c r="B23" t="n">
+        <v>10.943</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10.943</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10.943</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B24" t="n">
+        <v>30.272</v>
+      </c>
+      <c r="C24" t="n">
+        <v>30.272</v>
+      </c>
+      <c r="D24" t="n">
+        <v>30.272</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>29</v>
+      </c>
+      <c r="B25" t="n">
+        <v>42.667</v>
+      </c>
+      <c r="C25" t="n">
+        <v>42.667</v>
+      </c>
+      <c r="D25" t="n">
+        <v>42.667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>30</v>
+      </c>
+      <c r="B26" t="n">
+        <v>29.794</v>
+      </c>
+      <c r="C26" t="n">
+        <v>29.794</v>
+      </c>
+      <c r="D26" t="n">
+        <v>29.794</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>31</v>
+      </c>
+      <c r="B27" t="n">
+        <v>53.617</v>
+      </c>
+      <c r="C27" t="n">
+        <v>53.617</v>
+      </c>
+      <c r="D27" t="n">
+        <v>53.617</v>
       </c>
     </row>
   </sheetData>
